--- a/cet4/result/85_豪门甜宠_霸总的职场娇妻/85_豪门甜宠_霸总的职场娇妻_学习版.xlsx
+++ b/cet4/result/85_豪门甜宠_霸总的职场娇妻/85_豪门甜宠_霸总的职场娇妻_学习版.xlsx
@@ -399,710 +399,710 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>collapse</v>
       </c>
       <c r="B2" t="str">
-        <v>collapse</v>
+        <v>/kəˈlæps/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>崩溃</v>
       </c>
-      <c r="D2" t="str">
-        <v>collapse(崩溃)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>privilege</v>
       </c>
       <c r="B3" t="str">
-        <v>privilege</v>
+        <v>/ˈprɪvəlɪdʒ/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>特权</v>
       </c>
-      <c r="D3" t="str">
-        <v>privilege(特权)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>kite</v>
       </c>
       <c r="B4" t="str">
-        <v>kite</v>
+        <v>/kaɪt/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>风筝</v>
       </c>
-      <c r="D4" t="str">
-        <v>kite(风筝)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>complicate</v>
       </c>
       <c r="B5" t="str">
-        <v>complicate</v>
+        <v>/ˈkɑːmplɪkeɪt/</v>
       </c>
       <c r="C5" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D5" t="str">
         <v>复杂</v>
       </c>
-      <c r="D5" t="str">
-        <v>complicate(复杂)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>refute</v>
       </c>
       <c r="B6" t="str">
-        <v>refute</v>
+        <v>/rɪˈfjuːt/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D6" t="str">
         <v>反驳</v>
       </c>
-      <c r="D6" t="str">
-        <v>refute(反驳)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>priest</v>
       </c>
       <c r="B7" t="str">
-        <v>priest</v>
+        <v>/priːst/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D7" t="str">
         <v>牧师</v>
       </c>
-      <c r="D7" t="str">
-        <v>priest(牧师)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>lighten</v>
       </c>
       <c r="B8" t="str">
-        <v>lighten</v>
+        <v>/ˈlaɪtn/</v>
       </c>
       <c r="C8" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>减轻</v>
       </c>
-      <c r="D8" t="str">
-        <v>lighten(减轻)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>shiver</v>
       </c>
       <c r="B9" t="str">
-        <v>shiver</v>
+        <v>/ˈʃɪvər/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>颤抖</v>
       </c>
-      <c r="D9" t="str">
-        <v>shiver(颤抖)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>toilet</v>
       </c>
       <c r="B10" t="str">
-        <v>toilet</v>
+        <v>/ˈtɔɪlət/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>洗手间</v>
       </c>
-      <c r="D10" t="str">
-        <v>toilet(洗手间)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>organic</v>
       </c>
       <c r="B11" t="str">
-        <v>organic</v>
+        <v>/ɔːrˈɡænɪk/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>有机的</v>
       </c>
-      <c r="D11" t="str">
-        <v>organic(有机的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>interpretation</v>
       </c>
       <c r="B12" t="str">
-        <v>interpretation</v>
+        <v>/ɪnˌtɜːrprəˈteɪʃn/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>解释</v>
       </c>
-      <c r="D12" t="str">
-        <v>interpretation(解释)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>admission</v>
       </c>
       <c r="B13" t="str">
-        <v>admission</v>
+        <v>/ədˈmɪʃn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>入场许可</v>
       </c>
-      <c r="D13" t="str">
-        <v>admission(入场许可)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>duration</v>
       </c>
       <c r="B14" t="str">
-        <v>duration</v>
+        <v>/duˈreɪʃn/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>期间</v>
       </c>
-      <c r="D14" t="str">
-        <v>duration(期间)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>they</v>
       </c>
       <c r="B15" t="str">
-        <v>they</v>
+        <v>/ðeɪ/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D15" t="str">
         <v>他们</v>
       </c>
-      <c r="D15" t="str">
-        <v>they(他们)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>rubber</v>
       </c>
       <c r="B16" t="str">
-        <v>rubber</v>
+        <v>/ˈrʌbər/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>橡胶</v>
       </c>
-      <c r="D16" t="str">
-        <v>rubber(橡胶)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>compile</v>
       </c>
       <c r="B17" t="str">
-        <v>compile</v>
+        <v>/kəmˈpaɪl/</v>
       </c>
       <c r="C17" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D17" t="str">
         <v>编译</v>
       </c>
-      <c r="D17" t="str">
-        <v>compile(编译)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>compel</v>
       </c>
       <c r="B18" t="str">
-        <v>compel</v>
+        <v>/kəmˈpel/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>强迫</v>
       </c>
-      <c r="D18" t="str">
-        <v>compel(强迫)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>scare</v>
       </c>
       <c r="B19" t="str">
-        <v>scare</v>
+        <v>/sker/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>惊吓</v>
       </c>
-      <c r="D19" t="str">
-        <v>scare(惊吓)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>plant</v>
       </c>
       <c r="B20" t="str">
-        <v>plant</v>
+        <v>/plænt/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>工厂</v>
       </c>
-      <c r="D20" t="str">
-        <v>plant(工厂)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>inferior</v>
       </c>
       <c r="B21" t="str">
-        <v>inferior</v>
+        <v>/ɪnˈfɪriər/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>低等的</v>
       </c>
-      <c r="D21" t="str">
-        <v>inferior(低等的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>lens</v>
       </c>
       <c r="B22" t="str">
-        <v>lens</v>
+        <v>/lenz/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D22" t="str">
         <v>镜片</v>
       </c>
-      <c r="D22" t="str">
-        <v>lens(镜片)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>uneasy</v>
       </c>
       <c r="B23" t="str">
-        <v>uneasy</v>
+        <v>/ʌnˈiːzi/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>不安</v>
       </c>
-      <c r="D23" t="str">
-        <v>uneasy(不安)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>textile</v>
       </c>
       <c r="B24" t="str">
-        <v>textile</v>
+        <v>/ˈtekstaɪl/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>纺织品</v>
       </c>
-      <c r="D24" t="str">
-        <v>textile(纺织品)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>bench</v>
       </c>
       <c r="B25" t="str">
-        <v>bench</v>
+        <v>/bentʃ/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D25" t="str">
         <v>长凳</v>
       </c>
-      <c r="D25" t="str">
-        <v>bench(长凳)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>glow</v>
       </c>
       <c r="B26" t="str">
-        <v>glow</v>
+        <v>/ɡloʊ/</v>
       </c>
       <c r="C26" t="str">
+        <v>vi.</v>
+      </c>
+      <c r="D26" t="str">
         <v>发光</v>
       </c>
-      <c r="D26" t="str">
-        <v>glow(发光)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>bough</v>
       </c>
       <c r="B27" t="str">
-        <v>bough</v>
+        <v>/baʊ/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>大树枝</v>
       </c>
-      <c r="D27" t="str">
-        <v>bough(大树枝)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>put</v>
       </c>
       <c r="B28" t="str">
-        <v>put</v>
+        <v>/pʊt/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>放下</v>
       </c>
-      <c r="D28" t="str">
-        <v>put(放下)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>chase</v>
       </c>
       <c r="B29" t="str">
-        <v>chase</v>
+        <v>/tʃeɪs/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D29" t="str">
         <v>追逐</v>
       </c>
-      <c r="D29" t="str">
-        <v>chase(追逐)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>key</v>
       </c>
       <c r="B30" t="str">
-        <v>key</v>
+        <v>/kiː/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D30" t="str">
         <v>钥匙</v>
       </c>
-      <c r="D30" t="str">
-        <v>key(钥匙)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>change</v>
       </c>
       <c r="B31" t="str">
-        <v>change</v>
+        <v>/tʃeɪndʒ/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D31" t="str">
         <v>改变</v>
       </c>
-      <c r="D31" t="str">
-        <v>change(改变)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>used</v>
       </c>
       <c r="B32" t="str">
-        <v>used</v>
+        <v>/juːst; juːzd/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>习惯</v>
       </c>
-      <c r="D32" t="str">
-        <v>used(习惯)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>reporter</v>
       </c>
       <c r="B33" t="str">
-        <v>reporter</v>
+        <v>/rɪˈpɔːrtər/</v>
       </c>
       <c r="C33" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>记者</v>
       </c>
-      <c r="D33" t="str">
-        <v>reporter(记者)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>seller</v>
       </c>
       <c r="B34" t="str">
-        <v>seller</v>
+        <v>/ˈselər/</v>
       </c>
       <c r="C34" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>销售员</v>
       </c>
-      <c r="D34" t="str">
-        <v>seller(销售员)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>fertilize</v>
       </c>
       <c r="B35" t="str">
-        <v>fertilize</v>
+        <v>/ˈfɜːrtəlaɪz/</v>
       </c>
       <c r="C35" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D35" t="str">
         <v>使肥沃</v>
       </c>
-      <c r="D35" t="str">
-        <v>fertilize(使肥沃)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>apology</v>
       </c>
       <c r="B36" t="str">
-        <v>apology</v>
+        <v>/əˈpɑːlədʒi/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>道歉</v>
       </c>
-      <c r="D36" t="str">
-        <v>apology(道歉)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>victim</v>
       </c>
       <c r="B37" t="str">
-        <v>victim</v>
+        <v>/ˈvɪktɪm/</v>
       </c>
       <c r="C37" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>受害者</v>
       </c>
-      <c r="D37" t="str">
-        <v>victim(受害者)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>fifty</v>
       </c>
       <c r="B38" t="str">
-        <v>fifty</v>
+        <v>/ˈfɪfti/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>五十</v>
       </c>
-      <c r="D38" t="str">
-        <v>fifty(五十)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>cancel</v>
       </c>
       <c r="B39" t="str">
-        <v>cancel</v>
+        <v>/ˈkænsl/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D39" t="str">
         <v>取消</v>
       </c>
-      <c r="D39" t="str">
-        <v>cancel(取消)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>plaster</v>
       </c>
       <c r="B40" t="str">
-        <v>plaster</v>
+        <v>/ˈplæstər/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D40" t="str">
         <v>石膏</v>
       </c>
-      <c r="D40" t="str">
-        <v>plaster(石膏)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>though</v>
       </c>
       <c r="B41" t="str">
-        <v>though</v>
+        <v>/ðoʊ/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./adv./conj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>虽然</v>
       </c>
-      <c r="D41" t="str">
-        <v>though(虽然)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>eat</v>
       </c>
       <c r="B42" t="str">
-        <v>eat</v>
+        <v>/iːt/</v>
       </c>
       <c r="C42" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D42" t="str">
         <v>进食</v>
       </c>
-      <c r="D42" t="str">
-        <v>eat(进食)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>writing</v>
       </c>
       <c r="B43" t="str">
-        <v>writing</v>
+        <v>/ˈraɪtɪŋ/</v>
       </c>
       <c r="C43" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D43" t="str">
         <v>书写</v>
       </c>
-      <c r="D43" t="str">
-        <v>writing(书写)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>hunger</v>
       </c>
       <c r="B44" t="str">
-        <v>hunger</v>
+        <v>/ˈhʌŋɡər/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D44" t="str">
         <v>渴望</v>
       </c>
-      <c r="D44" t="str">
-        <v>hunger(渴望)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>sake</v>
       </c>
       <c r="B45" t="str">
-        <v>sake</v>
+        <v>/seɪk; ˈsɑːki/</v>
       </c>
       <c r="C45" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>缘故</v>
       </c>
-      <c r="D45" t="str">
-        <v>sake(缘故)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>tub</v>
       </c>
       <c r="B46" t="str">
-        <v>tub</v>
+        <v>/tʌb/</v>
       </c>
       <c r="C46" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D46" t="str">
         <v>浴盆</v>
       </c>
-      <c r="D46" t="str">
-        <v>tub(浴盆)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>seldom</v>
       </c>
       <c r="B47" t="str">
-        <v>seldom</v>
+        <v>/ˈseldəm/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D47" t="str">
         <v>很少</v>
       </c>
-      <c r="D47" t="str">
-        <v>seldom(很少)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>prevent</v>
       </c>
       <c r="B48" t="str">
-        <v>prevent</v>
+        <v>/prɪˈvent/</v>
       </c>
       <c r="C48" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D48" t="str">
         <v>防止</v>
       </c>
-      <c r="D48" t="str">
-        <v>prevent(防止)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>same</v>
       </c>
       <c r="B49" t="str">
-        <v>same</v>
+        <v>/seɪm/</v>
       </c>
       <c r="C49" t="str">
+        <v>n./v./adj./adv./pron.</v>
+      </c>
+      <c r="D49" t="str">
         <v>相同的</v>
       </c>
-      <c r="D49" t="str">
-        <v>same(相同的)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>coward</v>
       </c>
       <c r="B50" t="str">
-        <v>coward</v>
+        <v>/ˈkaʊərd/</v>
       </c>
       <c r="C50" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D50" t="str">
         <v>懦夫</v>
-      </c>
-      <c r="D50" t="str">
-        <v>coward(懦夫)📢</v>
       </c>
     </row>
   </sheetData>
